--- a/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2022_o_higgins.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_mean_m_2022_o_higgins.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:44</t>
+    <t xml:space="preserve">2026-10-05 02:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>267460.88</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>307926.12</v>
+        <v>307926.13</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>275595.12</v>
+        <v>275595.13</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>312736.5</v>
@@ -745,7 +745,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>256759.12</v>
+        <v>256759.13</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>304998.72</v>
@@ -833,7 +833,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>282749.12</v>
+        <v>282749.13</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>330372.03</v>
@@ -847,7 +847,7 @@
         <v>277693.75</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>324105.12</v>
+        <v>324105.13</v>
       </c>
     </row>
     <row r="16">
@@ -913,7 +913,7 @@
         <v>273935.66</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>329863.62</v>
+        <v>329863.63</v>
       </c>
     </row>
     <row r="22">
@@ -1020,7 +1020,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>256654.62</v>
+        <v>256654.63</v>
       </c>
       <c r="C31" s="2" t="n">
         <v>304271.59</v>
@@ -1130,7 +1130,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>289466.12</v>
+        <v>289466.13</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>338820.44</v>
@@ -1287,7 +1287,7 @@
         <v>328020.5</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>391178.62</v>
+        <v>391178.63</v>
       </c>
     </row>
     <row r="56">
@@ -1372,7 +1372,7 @@
         <v>64</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>367974.12</v>
+        <v>367974.13</v>
       </c>
       <c r="C63" s="2" t="n">
         <v>422267.97</v>
@@ -1427,7 +1427,7 @@
         <v>69</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>362357.62</v>
+        <v>362357.63</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>432127.41</v>
@@ -1529,7 +1529,7 @@
         <v>377419.81</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>440497.12</v>
+        <v>440497.13</v>
       </c>
     </row>
     <row r="78">
@@ -1559,7 +1559,7 @@
         <v>81</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>380054.62</v>
+        <v>380054.63</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>446665.91</v>
@@ -1595,7 +1595,7 @@
         <v>386513.25</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>451935.62</v>
+        <v>451935.63</v>
       </c>
     </row>
     <row r="84">
